--- a/data/trans_dic/P79$hipoteca_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P79$hipoteca_2023-Edad-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,2</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,12</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,08</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,12</t>
+          <t>0,2; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,01</t>
+          <t>0,5; 1,93</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,94</t>
+          <t>0,62; 2,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,49</t>
+          <t>0,79; 2,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,39</t>
+          <t>0,98; 2,4</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,91</t>
+          <t>0,65; 2,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,52</t>
+          <t>0,35; 1,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,42</t>
+          <t>0,6; 1,64</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,4</t>
+          <t>0,41; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,78</t>
+          <t>0,56; 1,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,71</t>
+          <t>0,59; 1,77</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,6</t>
+          <t>0,17; 1,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,72</t>
+          <t>0,12; 0,87</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,29</t>
+          <t>0,69; 1,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,91</t>
+          <t>0,51; 0,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,0</t>
+          <t>0,66; 1,11</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 733</t>
+          <t>0; 9159</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>0; 10939</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10103</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1607; 12818</t>
+          <t>1507; 13271</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>922; 9098</t>
+          <t>966; 9642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4273; 17027</t>
+          <t>4782; 18446</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>18272</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4130; 15372</t>
+          <t>3730; 17377</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3859; 14394</t>
+          <t>4768; 15239</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10033; 26274</t>
+          <t>11778; 28875</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>14685</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2136; 16669</t>
+          <t>4405; 17485</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2566; 10538</t>
+          <t>2508; 10056</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6432; 22317</t>
+          <t>8377; 22993</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12342</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2585; 13053</t>
+          <t>2446; 13364</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2393; 9334</t>
+          <t>3289; 10848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6106; 18318</t>
+          <t>6912; 20858</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3049</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>632; 5773</t>
+          <t>693; 6997</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2631</t>
+          <t>0; 3093</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>569; 6864</t>
+          <t>1014; 7139</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19735; 43492</t>
+          <t>23716; 48897</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15615; 31908</t>
+          <t>18330; 35539</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40136; 68994</t>
+          <t>46623; 77646</t>
         </is>
       </c>
     </row>
